--- a/2026_금융보증_통합_사업계획.xlsx
+++ b/2026_금융보증_통합_사업계획.xlsx
@@ -5609,51 +5609,51 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>B28+B29</f>
+        <f>B28+B29+B30</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>C28+C29</f>
+        <f>C28+C29+C30</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>D28+D29</f>
+        <f>D28+D29+D30</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>E28+E29</f>
+        <f>E28+E29+E30</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>F28+F29</f>
+        <f>F28+F29+F30</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>G28+G29</f>
+        <f>G28+G29+G30</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>H28+H29</f>
+        <f>H28+H29+H30</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>I28+I29</f>
+        <f>I28+I29+I30</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>J28+J29</f>
+        <f>J28+J29+J30</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>K28+K29</f>
+        <f>K28+K29+K30</f>
         <v/>
       </c>
       <c r="L27" s="16">
-        <f>L28+L29</f>
+        <f>L28+L29+L30</f>
         <v/>
       </c>
       <c r="M27" s="16">
-        <f>M28+M29</f>
+        <f>M28+M29+M30</f>
         <v/>
       </c>
       <c r="N27" s="16">
@@ -5756,48 +5756,48 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>수입 EW 가입 건수</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      수입 EW 가입</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="6" t="n">
         <v>50.12170237</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="6" t="n">
         <v>86.57384954</v>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="6" t="n">
         <v>106.7297427</v>
       </c>
-      <c r="H30" s="16" t="n">
+      <c r="H30" s="6" t="n">
         <v>114.6634453</v>
       </c>
-      <c r="I30" s="16" t="n">
+      <c r="I30" s="6" t="n">
         <v>115.7891734</v>
       </c>
-      <c r="J30" s="16" t="n">
+      <c r="J30" s="6" t="n">
         <v>107.2121976</v>
       </c>
-      <c r="K30" s="16" t="n">
+      <c r="K30" s="6" t="n">
         <v>101.8515877</v>
       </c>
-      <c r="L30" s="16" t="n">
+      <c r="L30" s="6" t="n">
         <v>101.3155267</v>
       </c>
-      <c r="M30" s="16" t="n">
+      <c r="M30" s="6" t="n">
         <v>100.2434047</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="6">
         <f>SUM(B30:M30)</f>
         <v/>
       </c>
